--- a/result/LOXL2_LUAD_Tables.xlsx
+++ b/result/LOXL2_LUAD_Tables.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
@@ -508,342 +509,328 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>  </t>
+          <t xml:space="preserve">  FEMALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>0.856</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FEMALE</t>
+          <t xml:space="preserve">  MALE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  MALE</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>111</v>
-      </c>
-      <c r="C8" t="n">
-        <v>113</v>
-      </c>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>112</v>
+      </c>
+      <c r="C9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C11" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" t="n">
-        <v>11</v>
-      </c>
+          <t>pathologic_M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pathologic_M</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>162</v>
+      </c>
+      <c r="C14" t="n">
+        <v>160</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.715</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>162</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>160</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.878</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>13</v>
-      </c>
-      <c r="C16" t="n">
-        <v>11</v>
-      </c>
+          <t>pathologic_N</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>pathologic_N</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>142</v>
+      </c>
+      <c r="C17" t="n">
+        <v>174</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>142</v>
+        <v>51</v>
       </c>
       <c r="C18" t="n">
-        <v>174</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
+          <t>pathologic_T</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>pathologic_T</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t xml:space="preserve">  1.0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>66</v>
+      </c>
+      <c r="C22" t="n">
+        <v>98</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1.0</t>
+          <t xml:space="preserve">  2.0</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="C23" t="n">
-        <v>98</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2.0</t>
+          <t xml:space="preserve">  3.0</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="C24" t="n">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3.0</t>
+          <t xml:space="preserve">  4.0</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4.0</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>14</v>
-      </c>
-      <c r="C26" t="n">
-        <v>4</v>
-      </c>
+          <t>SmokingStatus</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SmokingStatus</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+          <t xml:space="preserve">  0.0</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>82</v>
+      </c>
+      <c r="C27" t="n">
+        <v>77</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.630</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  0.0</t>
+          <t xml:space="preserve">  1.0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="C28" t="n">
-        <v>77</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.700</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1.0</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>164</v>
-      </c>
-      <c r="C29" t="n">
         <v>169</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -856,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,27 +869,52 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ITGB1expression</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>PLAURexpression</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>SNAI1expression</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>VEGFCexpression</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -929,27 +941,52 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.169</t>
+          <t>0.370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>0.309</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>-0.133</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-0.031</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>-0.041</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>-0.026</t>
         </is>
       </c>
     </row>
@@ -957,7 +994,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -968,27 +1005,52 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.630</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.490</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.489</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.703</t>
         </is>
       </c>
     </row>
@@ -1015,27 +1077,52 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.071</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.007</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>-0.016</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.074</t>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1130,7 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1054,34 +1141,59 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
+          <t>0.181</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.198</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.706</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.906</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.144</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.774</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.181</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.611</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1091,12 +1203,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-0.063</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.074</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1106,22 +1218,47 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.068</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.086</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.027</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1129,45 +1266,70 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.630</t>
+          <t>0.162</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.551</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.624</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>ITGB1expression</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1177,17 +1339,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.169</t>
+          <t>0.370</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.063</t>
+          <t>0.060</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1197,17 +1359,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-0.066</t>
         </is>
       </c>
     </row>
@@ -1215,45 +1402,70 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.198</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.250</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.337</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>PLAURexpression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1263,22 +1475,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.042</t>
+          <t>0.182</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-0.068</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1288,12 +1500,37 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.250</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-0.044</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-0.111</t>
         </is>
       </c>
     </row>
@@ -1301,45 +1538,70 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.130</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.326</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.109</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>SNAI1expression</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1349,27 +1611,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>-0.007</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>-0.086</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.363</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1379,7 +1641,32 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>0.233</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-0.066</t>
         </is>
       </c>
     </row>
@@ -1387,45 +1674,70 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.906</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.928</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.341</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>VEGFCexpression</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1435,37 +1747,62 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.038</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.040</t>
+          <t>-0.027</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.069</t>
+          <t>0.250</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.233</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>-0.055</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
     </row>
@@ -1473,40 +1810,745 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P-value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.490</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.551</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.427</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KrasExpression</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>-0.039</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-0.022</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.156</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.624</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.054</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0.501</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.452</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TP53Expression</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.133</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.072</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.099</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.128</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.408</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.112</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.029</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.196</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.209</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0.940</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALKExpression</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.031</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-0.048</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-0.120</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-0.045</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.070</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-0.036</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-0.004</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.489</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.859</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.291</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.316</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.424</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BRAFExpression</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.041</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-0.044</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.018</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.080</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-0.040</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.368</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.326</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.078</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.940</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.372</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EGFR_Mut_Binary</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.042</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-0.066</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-0.111</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-0.066</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-0.055</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-0.102</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-0.050</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>0.107</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.703</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.865</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.337</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.109</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.341</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.427</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.469</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>0.122</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1519,7 +2561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1535,6 +2577,16 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>P-value</t>
         </is>
       </c>
@@ -1542,15 +2594,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
+          <t>ageG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.013</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0.202</t>
+        <v>1.485</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.023</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.157</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.038</t>
         </is>
       </c>
     </row>
@@ -1561,86 +2619,80 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>0.970</t>
+        <v>0.999</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.846</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LOXL2group_Low</t>
+          <t>pathologic_stage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0.073</t>
+        <v>1.463</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>LOXL2group_Low</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.276</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0.220</t>
+        <v>0.673</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.038</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>pathologic_stage_2.0</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.059</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>pathologic_stage_3.0</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.544</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>pathologic_stage_4.0</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2.692</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0.006</t>
+        <v>1.322</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.937</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.151</t>
         </is>
       </c>
     </row>
@@ -2586,4 +3638,99 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Survival Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Cancer Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Chi-square</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overall Survival (OS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LOXL2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>9.204</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Relapse-Free Survival (RFS)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LUAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LOXL2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2.020</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.155</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/result/LOXL2_LUAD_Tables.xlsx
+++ b/result/LOXL2_LUAD_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -894,27 +895,27 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>EGFRExpression</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>KrasExpression</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TP53Expression</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ALKExpression</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>BRAFExpression</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>EGFR_Mut_Binary</t>
         </is>
       </c>
     </row>
@@ -966,27 +967,27 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.299</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>0.021</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>-0.133</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>-0.031</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>-0.041</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>-0.026</t>
         </is>
       </c>
     </row>
@@ -1030,27 +1031,27 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>0.645</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>0.003</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>0.489</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>0.368</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.703</t>
         </is>
       </c>
     </row>
@@ -1102,27 +1103,27 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>-0.039</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>-0.016</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.042</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1167,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.837</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>0.482</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>0.408</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>0.859</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>0.774</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.611</t>
         </is>
       </c>
     </row>
@@ -1238,27 +1239,27 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>-0.001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>-0.022</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>0.072</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>-0.048</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>-0.050</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.012</t>
         </is>
       </c>
     </row>
@@ -1302,27 +1303,27 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>0.624</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>0.112</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>0.291</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>0.265</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.865</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1375,27 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.202</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>0.156</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>-0.099</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>-0.120</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>-0.091</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>-0.066</t>
         </is>
       </c>
     </row>
@@ -1443,22 +1444,22 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>0.029</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>0.008</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>0.043</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.337</t>
         </is>
       </c>
     </row>
@@ -1510,27 +1511,27 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>0.087</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>-0.045</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>-0.044</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>-0.111</t>
         </is>
       </c>
     </row>
@@ -1574,27 +1575,27 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>0.571</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>0.054</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>0.209</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>0.316</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>0.326</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.109</t>
         </is>
       </c>
     </row>
@@ -1646,27 +1647,27 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>-0.030</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>-0.128</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>-0.070</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>0.018</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>-0.066</t>
         </is>
       </c>
     </row>
@@ -1710,27 +1711,27 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>0.587</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>0.501</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>0.119</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>0.692</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.341</t>
         </is>
       </c>
     </row>
@@ -1782,27 +1783,27 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>0.041</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>-0.034</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>-0.058</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>-0.036</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>-0.102</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-0.055</t>
         </is>
       </c>
     </row>
@@ -1846,34 +1847,34 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
+          <t>0.369</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>0.452</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>0.196</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>0.424</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>0.024</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.427</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KrasExpression</t>
+          <t>EGFRExpression</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1883,37 +1884,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-0.039</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>-0.001</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>-0.026</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.030</t>
+          <t>0.025</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-0.034</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1923,22 +1924,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-0.057</t>
+          <t>0.011</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
     </row>
@@ -1951,17 +1952,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>0.983</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1971,45 +1972,45 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.571</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.587</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>0.369</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TP53Expression</t>
+          <t>KrasExpression</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2019,62 +2020,62 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.133</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>-0.039</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>-0.022</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.099</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.030</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>-0.057</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-0.128</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-0.058</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-0.057</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
     </row>
@@ -2087,65 +2088,65 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>0.645</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.408</t>
+          <t>0.482</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.624</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>&lt;0.001</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.054</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.452</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.810</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ALKExpression</t>
+          <t>TP53Expression</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2155,62 +2156,62 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.031</t>
+          <t>-0.133</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.010</t>
+          <t>0.046</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-0.048</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.120</t>
+          <t>-0.099</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.045</t>
+          <t>-0.057</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.070</t>
+          <t>-0.128</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-0.036</t>
+          <t>-0.058</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.004</t>
+          <t>-0.123</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>-0.057</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>0.067</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>-0.040</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
     </row>
@@ -2223,65 +2224,65 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>0.408</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.029</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.004</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>0.007</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BRAFExpression</t>
+          <t>ALKExpression</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2291,62 +2292,62 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.041</t>
+          <t>-0.031</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-0.016</t>
+          <t>0.010</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.048</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.091</t>
+          <t>-0.120</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.044</t>
+          <t>-0.045</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-0.070</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>-0.036</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.080</t>
+          <t>-0.024</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>-0.004</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>0.067</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>-0.040</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>0.107</t>
         </is>
       </c>
     </row>
@@ -2359,65 +2360,65 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.489</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.008</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.424</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>0.595</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.940</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EGFR_Mut_Binary</t>
+          <t>BRAFExpression</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2427,57 +2428,57 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.026</t>
+          <t>-0.041</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-0.016</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-0.050</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>-0.091</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.111</t>
+          <t>-0.044</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.066</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.055</t>
+          <t>-0.102</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-0.102</t>
+          <t>0.061</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.080</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.050</t>
+          <t>-0.003</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>-0.040</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2495,57 +2496,57 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.865</t>
+          <t>0.265</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>0.043</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>0.024</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.078</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.372</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -2561,7 +2562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2577,15 +2578,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2594,21 +2590,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age_at_initial_pathologic_diagnosis</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.485</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.023</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2.157</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.038</t>
+        <v>1.013</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.993-1.032</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.202</t>
         </is>
       </c>
     </row>
@@ -2619,80 +2614,116 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.846</t>
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.993-1.007</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.970</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>LOXL2group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.463</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1.225</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.746</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
+        <v>0.704</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.480-1.033</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.073</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LOXL2group_Low</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.673</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.038</t>
+        <v>1.276</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.864-1.885</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.220</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.903</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.937</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.151</t>
+        <v>2.059</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1.301-3.259</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.544</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.564-4.138</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.692</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.331-5.444</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.006</t>
         </is>
       </c>
     </row>
@@ -2707,933 +2738,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
           <t>P-value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.994-1.032</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.178</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>LOXL2expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.993-1.007</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.968</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.469</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.230-1.754</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0259</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>LOXL2group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.467-0.987</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.0242e-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1498.0037</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-106.4074</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3102.4148</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.067</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>225.6179</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-262.9497</v>
-      </c>
-      <c r="D9" t="n">
-        <v>714.1855</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.364</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>442.8355</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-144.2395</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1029.9106</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.139</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>720.606</v>
-      </c>
-      <c r="C11" t="n">
-        <v>66.2675</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1374.9446</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.031</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-283.4505</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1374.2909</v>
-      </c>
-      <c r="D12" t="n">
-        <v>807.3899</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.610</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-9.2821</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-32.9869</v>
-      </c>
-      <c r="D13" t="n">
-        <v>14.4226</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.442</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2.8753</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-5.9695</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.7201</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.523</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LOXL2expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0557</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>4.5391e-03</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1250.014</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-324.6758</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2824.7038</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.119</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>210.6152</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-272.1504</v>
-      </c>
-      <c r="D23" t="n">
-        <v>693.3808</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.391</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>331.8812</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-182.993</v>
-      </c>
-      <c r="D24" t="n">
-        <v>846.7554</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.206</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>469.7984</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-398.6164</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1338.2131</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.288</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>2551.5376</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1323.9678</v>
-      </c>
-      <c r="D26" t="n">
-        <v>3779.1074</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>&lt;0.001</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>-5.9705</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-28.9454</v>
-      </c>
-      <c r="D27" t="n">
-        <v>17.0044</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.610</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.1983</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-7.4503</v>
-      </c>
-      <c r="D28" t="n">
-        <v>9.847</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.785</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LOXL2expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0204</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3.5372e-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1540.4159</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-68.9648</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3149.7966</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.061</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>233.666</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-257.4589</v>
-      </c>
-      <c r="D37" t="n">
-        <v>724.7909</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.350</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>388.6574</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-231.4286</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1008.7434</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.218</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>679.6734</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-14.1054</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1373.4523</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.055</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>232.0588</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-2830.1495</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3294.2671</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.882</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>-9.206899999999999</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-33.1664</v>
-      </c>
-      <c r="D41" t="n">
-        <v>14.7526</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.450</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.4761</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-6.447</v>
-      </c>
-      <c r="D42" t="n">
-        <v>11.3991</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.585</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>LOXL2expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0087</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>7.3231e-01</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1488.2523</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-639.2376</v>
-      </c>
-      <c r="D50" t="n">
-        <v>3615.7422</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>317.2317</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-342.3307</v>
-      </c>
-      <c r="D51" t="n">
-        <v>976.7942</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.344</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>-625.8374</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1878.6965</v>
-      </c>
-      <c r="D52" t="n">
-        <v>627.0216</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.326</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age_at_initial_pathologic_diagnosis</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>-3.5708</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-35.6204</v>
-      </c>
-      <c r="D53" t="n">
-        <v>28.4789</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.826</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1.8412</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-10.2993</v>
-      </c>
-      <c r="D54" t="n">
-        <v>13.9817</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.765</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.888-1.910</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.176</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3646,6 +2874,1047 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LOXL2expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0066</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5.3451e-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1732.366</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>173.324-3291.408</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.030</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>278.376</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-200.86-757.612</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.254</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-9.335000000000001</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-32.726-14.057</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.433</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-7.05-10.504</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.699</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LOXL2expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0259</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.0242e-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1498.004</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-106.407-3102.415</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0.067</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>225.618</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-262.95-714.186</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>0.364</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>442.836</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-144.24-1029.911</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0.139</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>720.606</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>66.267-1374.945</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-283.45</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-1374.291-807.39</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0.610</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-9.282</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-32.987-14.423</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0.442</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-5.969-11.72</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.523</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LOXL2expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0557</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.5391e-03</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1250.014</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-324.676-2824.704</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>0.119</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>210.615</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-272.15-693.381</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>0.391</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>331.881</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-182.993-846.755</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>0.206</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>469.798</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-398.616-1338.213</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>0.288</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2551.538</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1323.968-3779.107</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>&lt;0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-5.971</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>-28.945-17.004</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.610</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.198</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-7.45-9.847</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.785</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LOXL2expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0204</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3.5372e-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1540.416</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-68.965-3149.797</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.061</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>233.666</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-257.459-724.791</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.350</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>388.657</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-231.429-1008.743</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.218</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>679.673</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-14.105-1373.452</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>232.059</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-2830.149-3294.267</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.882</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>-9.207000000000001</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-33.166-14.753</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.450</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.476</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-6.447-11.399</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>0.585</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>LOXL2expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>LOXL2expression ~ age_at_initial_pathologic_diagnosis + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0087</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7.3231e-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1488.252</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>-639.238-3615.742</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>0.169</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>317.232</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-342.331-976.794</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>0.344</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>-625.837</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-1878.697-627.022</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>0.326</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age_at_initial_pathologic_diagnosis</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>-3.571</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-35.62-28.479</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>0.826</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-10.299-13.982</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>0.765</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/LOXL2_LUAD_Tables.xlsx
+++ b/result/LOXL2_LUAD_Tables.xlsx
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.204</t>
+          <t>11.430</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.010</t>
         </is>
       </c>
     </row>
@@ -3990,12 +3990,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.020</t>
+          <t>7.177</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.066</t>
         </is>
       </c>
     </row>
